--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,132 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123301195</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79355</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Asketjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>617410</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6974304</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på brandpåverkad vriden torraka</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg, Måns Svensson, Simon Selberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>123301195</v>
       </c>
       <c r="B3" t="n">
-        <v>79355</v>
+        <v>79358</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>123301195</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Måns Svensson, Simon Selberg</t>
+          <t>Simon Selberg, Måns Svensson, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>123301195</v>
       </c>
       <c r="B3" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Simon Selberg, Måns Svensson, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Måns Svensson, Simon Selberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>123301195</v>
       </c>
       <c r="B3" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>123301195</v>
       </c>
       <c r="B3" t="n">
-        <v>79364</v>
+        <v>79370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>123301195</v>
       </c>
       <c r="B3" t="n">
-        <v>79370</v>
+        <v>79375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2021 artfynd.xlsx
+++ b/artfynd/A 32102-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,132 +794,6 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>123301195</v>
-      </c>
-      <c r="B3" t="n">
-        <v>79375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Asketjärnsberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>617410</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6974304</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Härnösand</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Viksjö</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på brandpåverkad vriden torraka</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Linnéa Kjellberg, Måns Svensson, Simon Selberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
